--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -766,6 +766,15 @@
     <t>SkillAugmentConfig.xlsx</t>
   </si>
   <si>
+    <t>SkillAugmentOptionsConfigCategory</t>
+  </si>
+  <si>
+    <t>SkillAugmentOptionsConfig</t>
+  </si>
+  <si>
+    <t>SkillAugmentOptionsConfig.xlsx</t>
+  </si>
+  <si>
     <t>SkillBuffConfigCategory</t>
   </si>
   <si>
@@ -782,15 +791,6 @@
   </si>
   <si>
     <t>SkillConfig.xlsx</t>
-  </si>
-  <si>
-    <t>SkillSocketConfigCategory</t>
-  </si>
-  <si>
-    <t>SkillSocketConfig</t>
-  </si>
-  <si>
-    <t>SkillSocketConfig.xlsx</t>
   </si>
   <si>
     <t>SkillWeaponConfigCategory</t>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="313">
   <si>
     <t>##var</t>
   </si>
@@ -818,6 +818,42 @@
   </si>
   <si>
     <t>StoreSellConfig.xlsx</t>
+  </si>
+  <si>
+    <t>StoryChapterConfigCategory</t>
+  </si>
+  <si>
+    <t>StoryChapterConfig</t>
+  </si>
+  <si>
+    <t>StoryChapterConfig.xlsx</t>
+  </si>
+  <si>
+    <t>StoryChoiceConfigCategory</t>
+  </si>
+  <si>
+    <t>StoryChoiceConfig</t>
+  </si>
+  <si>
+    <t>StoryChoiceConfig.xlsx</t>
+  </si>
+  <si>
+    <t>StoryConfigCategory</t>
+  </si>
+  <si>
+    <t>StoryConfig</t>
+  </si>
+  <si>
+    <t>StoryConfig.xlsx</t>
+  </si>
+  <si>
+    <t>StoryEndingConfigCategory</t>
+  </si>
+  <si>
+    <t>StoryEndingConfig</t>
+  </si>
+  <si>
+    <t>StoryEndingConfig.xlsx</t>
   </si>
   <si>
     <t>TakeCardConfigCategory</t>
@@ -2083,7 +2119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -3727,6 +3763,74 @@
         <v>298</v>
       </c>
     </row>
+    <row r="94" spans="2:12">
+      <c r="B94" t="s">
+        <v>301</v>
+      </c>
+      <c r="C94" t="s">
+        <v>302</v>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" t="s">
+        <v>303</v>
+      </c>
+      <c r="L94" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12">
+      <c r="B95" t="s">
+        <v>304</v>
+      </c>
+      <c r="C95" t="s">
+        <v>305</v>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
+        <v>306</v>
+      </c>
+      <c r="L95" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="96" spans="2:12">
+      <c r="B96" t="s">
+        <v>307</v>
+      </c>
+      <c r="C96" t="s">
+        <v>308</v>
+      </c>
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" t="s">
+        <v>309</v>
+      </c>
+      <c r="L96" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="97" spans="2:12">
+      <c r="B97" t="s">
+        <v>310</v>
+      </c>
+      <c r="C97" t="s">
+        <v>311</v>
+      </c>
+      <c r="D97" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" t="s">
+        <v>312</v>
+      </c>
+      <c r="L97" t="s">
+        <v>310</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="314">
   <si>
     <t>##var</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>GlobalValueConfig.xlsx</t>
+  </si>
+  <si>
+    <t>one</t>
   </si>
   <si>
     <t>GuideConfigCategory</t>
@@ -2688,1147 +2691,1150 @@
       <c r="E30" t="s">
         <v>111</v>
       </c>
+      <c r="G30" t="s">
+        <v>112</v>
+      </c>
       <c r="L30" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="31" spans="2:12">
       <c r="B31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>115</v>
+      </c>
+      <c r="L31" t="s">
         <v>113</v>
-      </c>
-      <c r="D31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>114</v>
-      </c>
-      <c r="L31" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="32" spans="2:12">
       <c r="B32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>118</v>
+      </c>
+      <c r="L32" t="s">
         <v>116</v>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>117</v>
-      </c>
-      <c r="L32" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="33" spans="2:12">
       <c r="B33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>121</v>
+      </c>
+      <c r="L33" t="s">
         <v>119</v>
-      </c>
-      <c r="D33" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
-        <v>120</v>
-      </c>
-      <c r="L33" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="34" spans="2:12">
       <c r="B34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>124</v>
+      </c>
+      <c r="L34" t="s">
         <v>122</v>
-      </c>
-      <c r="D34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
-        <v>123</v>
-      </c>
-      <c r="L34" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="35" spans="2:12">
       <c r="B35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>127</v>
+      </c>
+      <c r="L35" t="s">
         <v>125</v>
-      </c>
-      <c r="D35" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>126</v>
-      </c>
-      <c r="L35" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="36" spans="2:12">
       <c r="B36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>130</v>
+      </c>
+      <c r="L36" t="s">
         <v>128</v>
-      </c>
-      <c r="D36" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>129</v>
-      </c>
-      <c r="L36" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="37" spans="2:12">
       <c r="B37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>133</v>
+      </c>
+      <c r="L37" t="s">
         <v>131</v>
-      </c>
-      <c r="D37" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
-        <v>132</v>
-      </c>
-      <c r="L37" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="38" spans="2:12">
       <c r="B38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>136</v>
+      </c>
+      <c r="L38" t="s">
         <v>134</v>
-      </c>
-      <c r="D38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
-        <v>135</v>
-      </c>
-      <c r="L38" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="39" spans="2:12">
       <c r="B39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>139</v>
+      </c>
+      <c r="L39" t="s">
         <v>137</v>
-      </c>
-      <c r="D39" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>138</v>
-      </c>
-      <c r="L39" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="40" spans="2:12">
       <c r="B40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>142</v>
+      </c>
+      <c r="L40" t="s">
         <v>140</v>
-      </c>
-      <c r="D40" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
-        <v>141</v>
-      </c>
-      <c r="L40" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="41" spans="2:12">
       <c r="B41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>145</v>
+      </c>
+      <c r="L41" t="s">
         <v>143</v>
-      </c>
-      <c r="D41" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>144</v>
-      </c>
-      <c r="L41" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="42" spans="2:12">
       <c r="B42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>148</v>
+      </c>
+      <c r="L42" t="s">
         <v>146</v>
-      </c>
-      <c r="D42" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>147</v>
-      </c>
-      <c r="L42" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="43" spans="2:12">
       <c r="B43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>151</v>
+      </c>
+      <c r="L43" t="s">
         <v>149</v>
-      </c>
-      <c r="D43" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>150</v>
-      </c>
-      <c r="L43" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="44" spans="2:12">
       <c r="B44" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C44" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>154</v>
+      </c>
+      <c r="L44" t="s">
         <v>152</v>
-      </c>
-      <c r="D44" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>153</v>
-      </c>
-      <c r="L44" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="45" spans="2:12">
       <c r="B45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C45" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
+        <v>157</v>
+      </c>
+      <c r="L45" t="s">
         <v>155</v>
-      </c>
-      <c r="D45" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s">
-        <v>156</v>
-      </c>
-      <c r="L45" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="46" spans="2:12">
       <c r="B46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C46" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>160</v>
+      </c>
+      <c r="L46" t="s">
         <v>158</v>
-      </c>
-      <c r="D46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" t="s">
-        <v>159</v>
-      </c>
-      <c r="L46" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="47" spans="2:12">
       <c r="B47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
+        <v>162</v>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>163</v>
+      </c>
+      <c r="L47" t="s">
         <v>161</v>
-      </c>
-      <c r="D47" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" t="s">
-        <v>162</v>
-      </c>
-      <c r="L47" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="48" spans="2:12">
       <c r="B48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>166</v>
+      </c>
+      <c r="L48" t="s">
         <v>164</v>
-      </c>
-      <c r="D48" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" t="s">
-        <v>165</v>
-      </c>
-      <c r="L48" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="49" spans="2:12">
       <c r="B49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C49" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
+        <v>169</v>
+      </c>
+      <c r="L49" t="s">
         <v>167</v>
-      </c>
-      <c r="D49" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" t="s">
-        <v>168</v>
-      </c>
-      <c r="L49" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="50" spans="2:12">
       <c r="B50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C50" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
+        <v>172</v>
+      </c>
+      <c r="L50" t="s">
         <v>170</v>
-      </c>
-      <c r="D50" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
-        <v>171</v>
-      </c>
-      <c r="L50" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="51" spans="2:12">
       <c r="B51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C51" t="s">
+        <v>174</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
+        <v>175</v>
+      </c>
+      <c r="L51" t="s">
         <v>173</v>
-      </c>
-      <c r="D51" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>174</v>
-      </c>
-      <c r="L51" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="52" spans="2:12">
       <c r="B52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C52" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>178</v>
+      </c>
+      <c r="L52" t="s">
         <v>176</v>
-      </c>
-      <c r="D52" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" t="s">
-        <v>177</v>
-      </c>
-      <c r="L52" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="53" spans="2:12">
       <c r="B53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>181</v>
+      </c>
+      <c r="L53" t="s">
         <v>179</v>
-      </c>
-      <c r="D53" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
-        <v>180</v>
-      </c>
-      <c r="L53" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="54" spans="2:12">
       <c r="B54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C54" t="s">
+        <v>183</v>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" t="s">
+        <v>184</v>
+      </c>
+      <c r="L54" t="s">
         <v>182</v>
-      </c>
-      <c r="D54" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" t="s">
-        <v>183</v>
-      </c>
-      <c r="L54" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="55" spans="2:12">
       <c r="B55" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C55" t="s">
+        <v>186</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>187</v>
+      </c>
+      <c r="L55" t="s">
         <v>185</v>
-      </c>
-      <c r="D55" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
-        <v>186</v>
-      </c>
-      <c r="L55" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="56" spans="2:12">
       <c r="B56" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C56" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>190</v>
+      </c>
+      <c r="L56" t="s">
         <v>188</v>
-      </c>
-      <c r="D56" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" t="s">
-        <v>189</v>
-      </c>
-      <c r="L56" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="57" spans="2:12">
       <c r="B57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C57" t="s">
+        <v>192</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" t="s">
+        <v>193</v>
+      </c>
+      <c r="L57" t="s">
         <v>191</v>
-      </c>
-      <c r="D57" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" t="s">
-        <v>192</v>
-      </c>
-      <c r="L57" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="58" spans="2:12">
       <c r="B58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C58" t="s">
+        <v>195</v>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>196</v>
+      </c>
+      <c r="L58" t="s">
         <v>194</v>
-      </c>
-      <c r="D58" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s">
-        <v>195</v>
-      </c>
-      <c r="L58" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="59" spans="2:12">
       <c r="B59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C59" t="s">
+        <v>198</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>199</v>
+      </c>
+      <c r="L59" t="s">
         <v>197</v>
-      </c>
-      <c r="D59" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
-        <v>198</v>
-      </c>
-      <c r="L59" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="60" spans="2:12">
       <c r="B60" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C60" t="s">
+        <v>201</v>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" t="s">
+        <v>202</v>
+      </c>
+      <c r="L60" t="s">
         <v>200</v>
-      </c>
-      <c r="D60" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" t="s">
-        <v>201</v>
-      </c>
-      <c r="L60" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="61" spans="2:12">
       <c r="B61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C61" t="s">
+        <v>204</v>
+      </c>
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>205</v>
+      </c>
+      <c r="L61" t="s">
         <v>203</v>
-      </c>
-      <c r="D61" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" t="s">
-        <v>204</v>
-      </c>
-      <c r="L61" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="62" spans="2:12">
       <c r="B62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C62" t="s">
+        <v>207</v>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L62" t="s">
         <v>206</v>
-      </c>
-      <c r="D62" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L62" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="63" spans="2:12">
       <c r="B63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C63" t="s">
+        <v>210</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>211</v>
+      </c>
+      <c r="L63" t="s">
         <v>209</v>
-      </c>
-      <c r="D63" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>210</v>
-      </c>
-      <c r="L63" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="64" spans="2:12">
       <c r="B64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C64" t="s">
+        <v>213</v>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>214</v>
+      </c>
+      <c r="L64" t="s">
         <v>212</v>
-      </c>
-      <c r="D64" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" t="s">
-        <v>213</v>
-      </c>
-      <c r="L64" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="65" spans="2:12">
       <c r="B65" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C65" t="s">
+        <v>216</v>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>217</v>
+      </c>
+      <c r="L65" t="s">
         <v>215</v>
-      </c>
-      <c r="D65" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s">
-        <v>216</v>
-      </c>
-      <c r="L65" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="66" spans="2:12">
       <c r="B66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C66" t="s">
+        <v>219</v>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
+        <v>220</v>
+      </c>
+      <c r="L66" t="s">
         <v>218</v>
-      </c>
-      <c r="D66" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s">
-        <v>219</v>
-      </c>
-      <c r="L66" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="67" spans="2:12">
       <c r="B67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C67" t="s">
+        <v>222</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" t="s">
+        <v>223</v>
+      </c>
+      <c r="L67" t="s">
         <v>221</v>
-      </c>
-      <c r="D67" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" t="s">
-        <v>222</v>
-      </c>
-      <c r="L67" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="68" spans="2:12">
       <c r="B68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C68" t="s">
+        <v>225</v>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
+        <v>226</v>
+      </c>
+      <c r="L68" t="s">
         <v>224</v>
-      </c>
-      <c r="D68" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" t="s">
-        <v>225</v>
-      </c>
-      <c r="L68" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="69" spans="2:12">
       <c r="B69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C69" t="s">
+        <v>228</v>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
+        <v>229</v>
+      </c>
+      <c r="L69" t="s">
         <v>227</v>
-      </c>
-      <c r="D69" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" t="s">
-        <v>228</v>
-      </c>
-      <c r="L69" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="70" spans="2:12">
       <c r="B70" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C70" t="s">
+        <v>231</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
+        <v>232</v>
+      </c>
+      <c r="L70" t="s">
         <v>230</v>
-      </c>
-      <c r="D70" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" t="s">
-        <v>231</v>
-      </c>
-      <c r="L70" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="71" spans="2:12">
       <c r="B71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C71" t="s">
+        <v>234</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>235</v>
+      </c>
+      <c r="L71" t="s">
         <v>233</v>
-      </c>
-      <c r="D71" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
-        <v>234</v>
-      </c>
-      <c r="L71" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="72" spans="2:12">
       <c r="B72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C72" t="s">
+        <v>237</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>238</v>
+      </c>
+      <c r="L72" t="s">
         <v>236</v>
-      </c>
-      <c r="D72" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
-        <v>237</v>
-      </c>
-      <c r="L72" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="73" spans="2:12">
       <c r="B73" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C73" t="s">
+        <v>240</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>241</v>
+      </c>
+      <c r="L73" t="s">
         <v>239</v>
-      </c>
-      <c r="D73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s">
-        <v>240</v>
-      </c>
-      <c r="L73" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="74" spans="2:12">
       <c r="B74" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C74" t="s">
+        <v>243</v>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>244</v>
+      </c>
+      <c r="L74" t="s">
         <v>242</v>
-      </c>
-      <c r="D74" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
-        <v>243</v>
-      </c>
-      <c r="L74" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="75" spans="2:12">
       <c r="B75" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C75" t="s">
+        <v>246</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>247</v>
+      </c>
+      <c r="L75" t="s">
         <v>245</v>
-      </c>
-      <c r="D75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>246</v>
-      </c>
-      <c r="L75" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="76" spans="2:12">
       <c r="B76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C76" t="s">
+        <v>249</v>
+      </c>
+      <c r="D76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>250</v>
+      </c>
+      <c r="L76" t="s">
         <v>248</v>
-      </c>
-      <c r="D76" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" t="s">
-        <v>249</v>
-      </c>
-      <c r="L76" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="77" spans="2:12">
       <c r="B77" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C77" t="s">
+        <v>252</v>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>253</v>
+      </c>
+      <c r="L77" t="s">
         <v>251</v>
-      </c>
-      <c r="D77" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" t="s">
-        <v>252</v>
-      </c>
-      <c r="L77" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="78" spans="2:12">
       <c r="B78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C78" t="s">
+        <v>255</v>
+      </c>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>256</v>
+      </c>
+      <c r="L78" t="s">
         <v>254</v>
-      </c>
-      <c r="D78" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" t="s">
-        <v>255</v>
-      </c>
-      <c r="L78" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="79" spans="2:12">
       <c r="B79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C79" t="s">
+        <v>258</v>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L79" t="s">
         <v>257</v>
-      </c>
-      <c r="D79" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" t="s">
-        <v>258</v>
-      </c>
-      <c r="L79" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="80" spans="2:12">
       <c r="B80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C80" t="s">
+        <v>261</v>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>262</v>
+      </c>
+      <c r="L80" t="s">
         <v>260</v>
-      </c>
-      <c r="D80" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" t="s">
-        <v>261</v>
-      </c>
-      <c r="L80" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="81" spans="2:12">
       <c r="B81" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C81" t="s">
+        <v>264</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
+        <v>265</v>
+      </c>
+      <c r="L81" t="s">
         <v>263</v>
-      </c>
-      <c r="D81" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" t="s">
-        <v>264</v>
-      </c>
-      <c r="L81" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="82" spans="2:12">
       <c r="B82" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C82" t="s">
+        <v>267</v>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
+        <v>268</v>
+      </c>
+      <c r="L82" t="s">
         <v>266</v>
-      </c>
-      <c r="D82" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" t="s">
-        <v>267</v>
-      </c>
-      <c r="L82" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="83" spans="2:12">
       <c r="B83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C83" t="s">
+        <v>270</v>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" t="s">
+        <v>271</v>
+      </c>
+      <c r="L83" t="s">
         <v>269</v>
-      </c>
-      <c r="D83" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" t="s">
-        <v>270</v>
-      </c>
-      <c r="L83" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="84" spans="2:12">
       <c r="B84" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C84" t="s">
+        <v>273</v>
+      </c>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" t="s">
+        <v>274</v>
+      </c>
+      <c r="L84" t="s">
         <v>272</v>
-      </c>
-      <c r="D84" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" t="s">
-        <v>273</v>
-      </c>
-      <c r="L84" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="85" spans="2:12">
       <c r="B85" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C85" t="s">
+        <v>276</v>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>277</v>
+      </c>
+      <c r="L85" t="s">
         <v>275</v>
-      </c>
-      <c r="D85" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" t="s">
-        <v>276</v>
-      </c>
-      <c r="L85" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="86" spans="2:12">
       <c r="B86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C86" t="s">
+        <v>279</v>
+      </c>
+      <c r="D86" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>280</v>
+      </c>
+      <c r="L86" t="s">
         <v>278</v>
-      </c>
-      <c r="D86" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" t="s">
-        <v>279</v>
-      </c>
-      <c r="L86" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="87" spans="2:12">
       <c r="B87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C87" t="s">
+        <v>282</v>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" t="s">
+        <v>283</v>
+      </c>
+      <c r="L87" t="s">
         <v>281</v>
-      </c>
-      <c r="D87" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" t="s">
-        <v>282</v>
-      </c>
-      <c r="L87" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="88" spans="2:12">
       <c r="B88" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C88" t="s">
+        <v>285</v>
+      </c>
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" t="s">
+        <v>286</v>
+      </c>
+      <c r="L88" t="s">
         <v>284</v>
-      </c>
-      <c r="D88" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" t="s">
-        <v>285</v>
-      </c>
-      <c r="L88" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="89" spans="2:12">
       <c r="B89" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C89" t="s">
+        <v>288</v>
+      </c>
+      <c r="D89" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" t="s">
+        <v>289</v>
+      </c>
+      <c r="L89" t="s">
         <v>287</v>
-      </c>
-      <c r="D89" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" t="s">
-        <v>288</v>
-      </c>
-      <c r="L89" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="90" spans="2:12">
       <c r="B90" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C90" t="s">
+        <v>291</v>
+      </c>
+      <c r="D90" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" t="s">
+        <v>292</v>
+      </c>
+      <c r="L90" t="s">
         <v>290</v>
-      </c>
-      <c r="D90" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" t="s">
-        <v>291</v>
-      </c>
-      <c r="L90" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="91" spans="2:12">
       <c r="B91" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C91" t="s">
+        <v>294</v>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" t="s">
+        <v>295</v>
+      </c>
+      <c r="L91" t="s">
         <v>293</v>
-      </c>
-      <c r="D91" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" t="s">
-        <v>294</v>
-      </c>
-      <c r="L91" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="92" spans="2:12">
       <c r="B92" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C92" t="s">
+        <v>297</v>
+      </c>
+      <c r="D92" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" t="s">
+        <v>298</v>
+      </c>
+      <c r="L92" t="s">
         <v>296</v>
-      </c>
-      <c r="D92" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" t="s">
-        <v>297</v>
-      </c>
-      <c r="L92" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="93" spans="2:12">
       <c r="B93" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C93" t="s">
+        <v>300</v>
+      </c>
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" t="s">
+        <v>301</v>
+      </c>
+      <c r="L93" t="s">
         <v>299</v>
-      </c>
-      <c r="D93" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" t="s">
-        <v>300</v>
-      </c>
-      <c r="L93" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="94" spans="2:12">
       <c r="B94" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C94" t="s">
+        <v>303</v>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" t="s">
+        <v>304</v>
+      </c>
+      <c r="L94" t="s">
         <v>302</v>
-      </c>
-      <c r="D94" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" t="s">
-        <v>303</v>
-      </c>
-      <c r="L94" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="95" spans="2:12">
       <c r="B95" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C95" t="s">
+        <v>306</v>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
+        <v>307</v>
+      </c>
+      <c r="L95" t="s">
         <v>305</v>
-      </c>
-      <c r="D95" t="b">
-        <v>1</v>
-      </c>
-      <c r="E95" t="s">
-        <v>306</v>
-      </c>
-      <c r="L95" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="96" spans="2:12">
       <c r="B96" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C96" t="s">
+        <v>309</v>
+      </c>
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" t="s">
+        <v>310</v>
+      </c>
+      <c r="L96" t="s">
         <v>308</v>
-      </c>
-      <c r="D96" t="b">
-        <v>1</v>
-      </c>
-      <c r="E96" t="s">
-        <v>309</v>
-      </c>
-      <c r="L96" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="97" spans="2:12">
       <c r="B97" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C97" t="s">
+        <v>312</v>
+      </c>
+      <c r="D97" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" t="s">
+        <v>313</v>
+      </c>
+      <c r="L97" t="s">
         <v>311</v>
-      </c>
-      <c r="D97" t="b">
-        <v>1</v>
-      </c>
-      <c r="E97" t="s">
-        <v>312</v>
-      </c>
-      <c r="L97" t="s">
-        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="317">
   <si>
     <t>##var</t>
   </si>
@@ -470,6 +470,15 @@
   </si>
   <si>
     <t>LingDiRewardConfig.xlsx</t>
+  </si>
+  <si>
+    <t>LongYinConfigCategory</t>
+  </si>
+  <si>
+    <t>LongYinConfig</t>
+  </si>
+  <si>
+    <t>LongYinConfig.xlsx</t>
   </si>
   <si>
     <t>MapObjectConfigCategory</t>
@@ -2122,7 +2131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -3837,6 +3846,23 @@
         <v>311</v>
       </c>
     </row>
+    <row r="98" spans="2:12">
+      <c r="B98" t="s">
+        <v>314</v>
+      </c>
+      <c r="C98" t="s">
+        <v>315</v>
+      </c>
+      <c r="D98" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" t="s">
+        <v>316</v>
+      </c>
+      <c r="L98" t="s">
+        <v>314</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="323">
   <si>
     <t>##var</t>
   </si>
@@ -359,6 +359,24 @@
   </si>
   <si>
     <t>FuntionConfig.xlsx</t>
+  </si>
+  <si>
+    <t>GemTalentAreaConfigCategory</t>
+  </si>
+  <si>
+    <t>GemTalentAreaConfig</t>
+  </si>
+  <si>
+    <t>GemTalentAreaConfig.xlsx</t>
+  </si>
+  <si>
+    <t>GemTalentConfigCategory</t>
+  </si>
+  <si>
+    <t>GemTalentConfig</t>
+  </si>
+  <si>
+    <t>GemTalentConfig.xlsx</t>
   </si>
   <si>
     <t>GlobalValueConfigCategory</t>
@@ -2131,7 +2149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -2700,45 +2718,45 @@
       <c r="E30" t="s">
         <v>111</v>
       </c>
-      <c r="G30" t="s">
-        <v>112</v>
-      </c>
       <c r="L30" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="31" spans="2:12">
       <c r="B31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" t="s">
         <v>113</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
         <v>114</v>
       </c>
-      <c r="D31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>115</v>
-      </c>
       <c r="L31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="2:12">
       <c r="B32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" t="s">
         <v>116</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
         <v>117</v>
       </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>118</v>
       </c>
       <c r="L32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -3861,6 +3879,40 @@
       </c>
       <c r="L98" t="s">
         <v>314</v>
+      </c>
+    </row>
+    <row r="99" spans="2:12">
+      <c r="B99" t="s">
+        <v>317</v>
+      </c>
+      <c r="C99" t="s">
+        <v>318</v>
+      </c>
+      <c r="D99" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" t="s">
+        <v>319</v>
+      </c>
+      <c r="L99" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="100" spans="2:12">
+      <c r="B100" t="s">
+        <v>320</v>
+      </c>
+      <c r="C100" t="s">
+        <v>321</v>
+      </c>
+      <c r="D100" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
+        <v>322</v>
+      </c>
+      <c r="L100" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
